--- a/이력번호.xlsx
+++ b/이력번호.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Sinnong\firstProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Sinnong\등판저장\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3E022C-D68A-4BFB-AA9A-A1A7698C7384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E565562-8A23-4783-A123-EFE03D943742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC1ED259-891A-4217-8A8F-979EBCC29542}"/>
   </bookViews>
@@ -36,37 +36,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>이력번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>002158205403</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>002177409652</t>
   </si>
   <si>
-    <t>002158206199</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>002167984505</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>002173370527</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>002174023091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>002175041876</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,13 +67,27 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55C8FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -105,11 +104,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,41 +448,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{943C0172-3CD0-4A53-853E-0857BC6AECCD}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
